--- a/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
+++ b/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="6" r:id="rId1"/>
@@ -28,7 +28,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="55" r:id="rId9"/>
+    <pivotCache cacheId="8" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -181,31 +181,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
-    </dxf>
+  <dxfs count="24">
     <dxf>
       <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
     </dxf>
@@ -310,7 +286,6 @@
   </c:pivotSource>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -575,7 +550,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -677,7 +651,6 @@
   </c:pivotSource>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -957,7 +930,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1059,7 +1031,6 @@
   </c:pivotSource>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1379,7 +1350,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3199,7 +3169,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="dserrada@gmail.com" refreshedDate="46273.742382638891" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="3">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshOnLoad="1" refreshedBy="dserrada@gmail.com" refreshedDate="46273.775013194441" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="3">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:G1048576" sheet="Datos"/>
   </cacheSource>
@@ -3305,7 +3275,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:C8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending" defaultSubtotal="0">
@@ -3399,7 +3369,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A4:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0" defaultSubtotal="0"/>
@@ -3463,16 +3433,16 @@
     <dataField name="Suma de precio" fld="6" baseField="1" baseItem="10" numFmtId="164"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="31">
+    <format dxfId="23">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="20">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -3503,7 +3473,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A4:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
@@ -3577,16 +3547,16 @@
     <dataField name="Suma de unidades" fld="2" baseField="7" baseItem="0" numFmtId="1"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="27">
+    <format dxfId="19">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="16">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -3617,7 +3587,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica4" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica4" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A7:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" showAll="0" sortType="descending" defaultSubtotal="0">
@@ -3716,7 +3686,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
@@ -3816,7 +3786,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica1" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" multipleItemSelectionAllowed="1" showAll="0" sortType="descending">
@@ -3902,7 +3872,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A6:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField axis="axisPage" showAll="0">

--- a/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
+++ b/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
@@ -3275,7 +3275,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="8" missingItemsLimit="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:C8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending" defaultSubtotal="0">
@@ -3473,7 +3473,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="8" missingItemsLimit="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A4:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
@@ -3587,7 +3587,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica4" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica4" cacheId="8" missingItemsLimit="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A7:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" showAll="0" sortType="descending" defaultSubtotal="0">
@@ -3686,7 +3686,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="8" missingItemsLimit="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
@@ -3786,7 +3786,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica1" cacheId="8" missingItemsLimit="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" multipleItemSelectionAllowed="1" showAll="0" sortType="descending">
@@ -3872,7 +3872,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="8" missingItemsLimit="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A6:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField axis="axisPage" showAll="0">

--- a/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
+++ b/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
@@ -3175,11 +3175,10 @@
   </cacheSource>
   <cacheFields count="8">
     <cacheField name="id" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="4" maxValue="4" count="4">
+      <sharedItems containsBlank="1" count="3">
         <s v="COCKTAIL RODEO"/>
         <s v="BARRA DE PAN"/>
         <m/>
-        <n v="4" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="fecha" numFmtId="14">
@@ -3279,8 +3278,7 @@
   <location ref="A4:C8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending" defaultSubtotal="0">
-      <items count="4">
-        <item m="1" x="3"/>
+      <items count="3">
         <item x="1"/>
         <item x="0"/>
         <item x="2"/>
@@ -3477,8 +3475,7 @@
   <location ref="A4:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
-      <items count="4">
-        <item m="1" x="3"/>
+      <items count="3">
         <item x="1"/>
         <item x="0"/>
         <item x="2"/>
@@ -3591,8 +3588,7 @@
   <location ref="A7:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" showAll="0" sortType="descending" defaultSubtotal="0">
-      <items count="4">
-        <item m="1" x="3"/>
+      <items count="3">
         <item x="1"/>
         <item x="0"/>
         <item x="2"/>
@@ -3690,8 +3686,7 @@
   <location ref="A4:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
-      <items count="5">
-        <item m="1" x="3"/>
+      <items count="4">
         <item x="1"/>
         <item x="0"/>
         <item x="2"/>
@@ -3790,8 +3785,7 @@
   <location ref="A4:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" multipleItemSelectionAllowed="1" showAll="0" sortType="descending">
-      <items count="5">
-        <item m="1" x="3"/>
+      <items count="4">
         <item x="1"/>
         <item x="0"/>
         <item x="2"/>
@@ -3876,8 +3870,7 @@
   <location ref="A6:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField axis="axisPage" showAll="0">
-      <items count="5">
-        <item m="1" x="3"/>
+      <items count="4">
         <item x="1"/>
         <item x="0"/>
         <item x="2"/>

--- a/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
+++ b/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="6" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Mes" sheetId="10" r:id="rId5"/>
     <sheet name="Año" sheetId="12" r:id="rId6"/>
     <sheet name="Último" sheetId="13" r:id="rId7"/>
-    <sheet name="Evol" sheetId="14" r:id="rId8"/>
+    <sheet name="Subida" sheetId="14" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Datos!$A$1:$G$3</definedName>
@@ -28,7 +28,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId9"/>
+    <pivotCache cacheId="9" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,8 +38,76 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>dserrada@gmail.com</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>dserrada@gmail.com:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Para que en un futuro se pueda estimar que producto está a punto de acabarse. Es decir lleva más tiempo del normal sin comprarse</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>dserrada@gmail.com</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>dserrada@gmail.com:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Se promedia al mes porque hay productos de temporada</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="28">
   <si>
     <t>BARRA DE PAN</t>
   </si>
@@ -95,34 +163,34 @@
     <t>Cuenta de id</t>
   </si>
   <si>
-    <t>Promedio de unidades</t>
-  </si>
-  <si>
-    <t>Número de veces que se ha comprado un producto</t>
-  </si>
-  <si>
-    <t>Evolución Gasto al mes</t>
-  </si>
-  <si>
     <t>(Todas)</t>
-  </si>
-  <si>
-    <t>Promedio de unidades de un producto compradas al mes</t>
-  </si>
-  <si>
-    <t>Número de productos comprados al año</t>
   </si>
   <si>
     <t>Máx. de fecha</t>
   </si>
   <si>
-    <t>Ultima vez que compré un producto</t>
+    <t>Suma de unidades</t>
   </si>
   <si>
-    <t>Evolución del precio de un producto promediado al mes</t>
+    <t>Listado de productos comprados agrupados por el número de veces comprado. Incluye promedios sobre el producto</t>
   </si>
   <si>
-    <t>Suma de unidades</t>
+    <t>Número de productos comprados al mes. Con gráfica</t>
+  </si>
+  <si>
+    <t>Dinero gastado al mes. Con gráfica</t>
+  </si>
+  <si>
+    <t>Ultima vez que se compró un producto</t>
+  </si>
+  <si>
+    <t>Evolución del precio de un producto promediado al mes. En el selector se fija el producto y permite ver como ha evolucionado su precio con el tiempo</t>
+  </si>
+  <si>
+    <t>Promedio por mes de unidades de un producto. Con selectores para fijar el producto y el mes</t>
+  </si>
+  <si>
+    <t>Número de productos comprados al año. Especie de bolsa de la compara anual. Muestra cuanto se ha gastado en ese producto al año</t>
   </si>
 </sst>
 </file>
@@ -132,13 +200,26 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -161,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -174,38 +255,11 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
     </dxf>
@@ -1026,11 +1080,12 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Mercadona-base.xlsx]Evol!TablaDinámica2</c:name>
+    <c:name>[Mercadona-base.xlsx]Subida!TablaDinámica2</c:name>
     <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1157,7 +1212,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Evol!$B$6</c:f>
+              <c:f>Subida!$B$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1180,7 +1235,7 @@
           </c:marker>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Evol!$A$7:$A$11</c:f>
+              <c:f>Subida!$A$7:$A$11</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="2"/>
                 <c:lvl>
@@ -1204,7 +1259,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Evol!$B$7:$B$11</c:f>
+              <c:f>Subida!$B$7:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -1350,6 +1405,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3169,7 +3225,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshOnLoad="1" refreshedBy="dserrada@gmail.com" refreshedDate="46273.775013194441" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="3">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshOnLoad="1" refreshedBy="dserrada@gmail.com" refreshedDate="46274.851091319448" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="3">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:G1048576" sheet="Datos"/>
   </cacheSource>
@@ -3274,7 +3330,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="8" missingItemsLimit="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:C8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending" defaultSubtotal="0">
@@ -3330,13 +3386,13 @@
   </rowFields>
   <rowItems count="4">
     <i>
+      <x/>
+    </i>
+    <i>
       <x v="1"/>
     </i>
     <i>
       <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -3367,7 +3423,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A4:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0" defaultSubtotal="0"/>
@@ -3431,16 +3487,16 @@
     <dataField name="Suma de precio" fld="6" baseField="1" baseItem="10" numFmtId="164"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="23">
+    <format dxfId="15">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="12">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -3471,7 +3527,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="8" missingItemsLimit="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A4:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
@@ -3544,16 +3600,16 @@
     <dataField name="Suma de unidades" fld="2" baseField="7" baseItem="0" numFmtId="1"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="19">
+    <format dxfId="11">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="8">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -3584,7 +3640,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica4" cacheId="8" missingItemsLimit="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica4" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A7:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" showAll="0" sortType="descending" defaultSubtotal="0">
@@ -3640,13 +3696,13 @@
   </rowFields>
   <rowItems count="4">
     <i>
-      <x v="2"/>
-    </i>
-    <i>
       <x v="1"/>
     </i>
     <i>
-      <x v="3"/>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -3659,7 +3715,7 @@
     <pageField fld="1" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Promedio de unidades" fld="2" subtotal="average" baseField="0" baseItem="9" numFmtId="1"/>
+    <dataField name="Suma de unidades" fld="2" baseField="0" baseItem="1" numFmtId="1"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="0" format="4" series="1">
@@ -3682,8 +3738,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="8" missingItemsLimit="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A4:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A4:C10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
       <items count="4">
@@ -3696,13 +3752,13 @@
         <pivotArea dataOnly="0" outline="0" fieldPosition="0">
           <references count="1">
             <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
+              <x v="1"/>
             </reference>
           </references>
         </pivotArea>
       </autoSortScope>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField showAll="0">
       <items count="15">
         <item x="0"/>
         <item x="1"/>
@@ -3725,7 +3781,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
     <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
       <items count="3">
         <item x="0"/>
@@ -3734,42 +3790,44 @@
       </items>
     </pivotField>
   </pivotFields>
-  <rowFields count="3">
+  <rowFields count="2">
     <field x="7"/>
-    <field x="1"/>
     <field x="0"/>
   </rowFields>
-  <rowItems count="8">
+  <rowItems count="6">
     <i>
       <x/>
     </i>
     <i r="1">
-      <x/>
-    </i>
-    <i r="2">
-      <x v="3"/>
+      <x v="2"/>
     </i>
     <i>
       <x v="1"/>
     </i>
     <i r="1">
-      <x v="6"/>
+      <x v="1"/>
     </i>
-    <i r="2">
-      <x v="2"/>
-    </i>
-    <i r="2">
-      <x v="1"/>
+    <i r="1">
+      <x/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
-  <colItems count="1">
-    <i/>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
   </colItems>
-  <dataFields count="1">
+  <dataFields count="2">
     <dataField name="Cuenta de id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Suma de precio" fld="6" baseField="0" baseItem="1"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -3781,7 +3839,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica1" cacheId="8" missingItemsLimit="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" multipleItemSelectionAllowed="1" showAll="0" sortType="descending">
@@ -3838,13 +3896,13 @@
   </rowFields>
   <rowItems count="4">
     <i>
+      <x/>
+    </i>
+    <i>
       <x v="1"/>
     </i>
     <i>
       <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -3866,7 +3924,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="8" missingItemsLimit="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A6:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField axis="axisPage" showAll="0">
@@ -4228,10 +4286,10 @@
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4310,7 +4368,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -6031,7 +6089,7 @@
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B1"/>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -19797,7 +19855,7 @@
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B1"/>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -19805,7 +19863,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -19813,7 +19871,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C4"/>
     </row>
@@ -33564,12 +33622,12 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -33577,7 +33635,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -33585,7 +33643,7 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -33615,7 +33673,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="7">
-        <v>1.5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -33625,16 +33683,17 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -33644,61 +33703,62 @@
       <c r="B4" t="s">
         <v>17</v>
       </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>3</v>
+      <c r="A7" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>6</v>
+      <c r="A8" s="5" t="s">
+        <v>1</v>
       </c>
-      <c r="B8" s="4"/>
+      <c r="B8" s="4">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B9" s="4">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="4">
-        <v>2</v>
+      <c r="C10" s="4">
+        <v>3.98</v>
       </c>
     </row>
   </sheetData>
@@ -33707,7 +33767,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -33717,7 +33777,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -33725,7 +33785,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -33761,11 +33821,12 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -33776,7 +33837,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -33784,7 +33845,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -33832,5 +33893,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
+++ b/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
@@ -9,17 +9,18 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="6" r:id="rId1"/>
     <sheet name="Productos" sheetId="7" r:id="rId2"/>
-    <sheet name="T_Precio" sheetId="8" r:id="rId3"/>
-    <sheet name="T_Cantidad" sheetId="15" r:id="rId4"/>
-    <sheet name="Mes" sheetId="10" r:id="rId5"/>
-    <sheet name="Año" sheetId="12" r:id="rId6"/>
-    <sheet name="Último" sheetId="13" r:id="rId7"/>
-    <sheet name="Subida" sheetId="14" r:id="rId8"/>
+    <sheet name="MiInflación" sheetId="16" r:id="rId3"/>
+    <sheet name="T_Precio" sheetId="8" r:id="rId4"/>
+    <sheet name="T_Cantidad" sheetId="15" r:id="rId5"/>
+    <sheet name="Mes" sheetId="10" r:id="rId6"/>
+    <sheet name="Año" sheetId="12" r:id="rId7"/>
+    <sheet name="Último" sheetId="13" r:id="rId8"/>
+    <sheet name="Subida" sheetId="14" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Datos!$A$1:$G$3</definedName>
@@ -28,7 +29,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId9"/>
+    <pivotCache cacheId="4" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -107,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="35">
   <si>
     <t>BARRA DE PAN</t>
   </si>
@@ -192,6 +193,27 @@
   <si>
     <t>Número de productos comprados al año. Especie de bolsa de la compara anual. Muestra cuanto se ha gastado en ese producto al año</t>
   </si>
+  <si>
+    <t>Esto se un cáculo de la inflación sufrida por los productos comprados. No es la inflación calculada por el INE</t>
+  </si>
+  <si>
+    <t>Año</t>
+  </si>
+  <si>
+    <t>Es año base</t>
+  </si>
+  <si>
+    <t>Completo</t>
+  </si>
+  <si>
+    <t>Laspeyres %</t>
+  </si>
+  <si>
+    <t>Paasche %</t>
+  </si>
+  <si>
+    <t>Productos coincidentes</t>
+  </si>
 </sst>
 </file>
 
@@ -242,7 +264,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -255,6 +277,7 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1085,7 +1108,6 @@
   </c:pivotSource>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1405,7 +1427,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3225,7 +3246,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshOnLoad="1" refreshedBy="dserrada@gmail.com" refreshedDate="46274.851091319448" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="3">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshOnLoad="1" refreshedBy="dserrada@gmail.com" refreshedDate="46275.604974768517" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="3">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:G1048576" sheet="Datos"/>
   </cacheSource>
@@ -3330,7 +3351,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:C8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending" defaultSubtotal="0">
@@ -3423,7 +3444,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A4:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0" defaultSubtotal="0"/>
@@ -3527,7 +3548,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A4:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
@@ -3640,7 +3661,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica4" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica4" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A7:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" showAll="0" sortType="descending" defaultSubtotal="0">
@@ -3738,7 +3759,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:C10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
@@ -3839,7 +3860,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" multipleItemSelectionAllowed="1" showAll="0" sortType="descending">
@@ -3924,7 +3945,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A6:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField axis="axisPage" showAll="0">
@@ -6078,6 +6099,44 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:F6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="21.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D3433"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -19842,7 +19901,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D3433"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -33616,7 +33675,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -33681,7 +33740,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -33766,7 +33825,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -33825,7 +33884,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
+++ b/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="6" r:id="rId1"/>
@@ -20,7 +20,8 @@
     <sheet name="Mes" sheetId="10" r:id="rId6"/>
     <sheet name="Año" sheetId="12" r:id="rId7"/>
     <sheet name="Último" sheetId="13" r:id="rId8"/>
-    <sheet name="Subida" sheetId="14" r:id="rId9"/>
+    <sheet name="Evolucion-€" sheetId="14" r:id="rId9"/>
+    <sheet name="Evolucion-N" sheetId="17" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Datos!$A$1:$G$3</definedName>
@@ -29,7 +30,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId10"/>
+    <pivotCache cacheId="4" r:id="rId11"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -108,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="36">
   <si>
     <t>BARRA DE PAN</t>
   </si>
@@ -213,6 +214,9 @@
   </si>
   <si>
     <t>Productos coincidentes</t>
+  </si>
+  <si>
+    <t>Evolución de la cantidad de productos comprados en un año. En el selector se fija el producto y permite ver como ha evolucionadoel número de productos comprados</t>
   </si>
 </sst>
 </file>
@@ -1103,11 +1107,12 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Mercadona-base.xlsx]Subida!TablaDinámica2</c:name>
+    <c:name>[Mercadona-base.xlsx]Evolucion-€!TablaDinámica2</c:name>
     <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1234,7 +1239,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Subida!$B$6</c:f>
+              <c:f>'Evolucion-€'!$B$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1257,7 +1262,7 @@
           </c:marker>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Subida!$A$7:$A$11</c:f>
+              <c:f>'Evolucion-€'!$A$7:$A$11</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="2"/>
                 <c:lvl>
@@ -1281,7 +1286,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Subida!$B$7:$B$11</c:f>
+              <c:f>'Evolucion-€'!$B$7:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -1427,6 +1432,368 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Mercadona-base.xlsx]Evolucion-N!TablaDinámica1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Evolucion-N'!$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Evolucion-N'!$A$7:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>&lt;16/06/2023</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Evolucion-N'!$B$7:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5B05-4E5C-82B9-86F8C05DAFB5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="557855232"/>
+        <c:axId val="557857312"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="557855232"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="557857312"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="557857312"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="557855232"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1590,6 +1957,46 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3138,6 +3545,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -3245,8 +4168,43 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshOnLoad="1" refreshedBy="dserrada@gmail.com" refreshedDate="46275.604974768517" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="3">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshOnLoad="1" refreshedBy="dserrada@gmail.com" refreshedDate="46277.655617592594" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="3">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:G1048576" sheet="Datos"/>
   </cacheSource>
@@ -4038,6 +4996,75 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A6:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="8">
+    <pivotField axis="axisPage" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="0" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Suma de unidades" fld="2" baseField="7" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
@@ -4377,6 +5404,64 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="4">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D558"/>

--- a/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
+++ b/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Productos" sheetId="7" r:id="rId2"/>
     <sheet name="Pareto" sheetId="18" r:id="rId15"/>
     <sheet name="MiInflación" sheetId="16" r:id="rId3"/>
+    <sheet name="Interanual" sheetId="19" r:id="rId16"/>
     <sheet name="T_Precio" sheetId="8" r:id="rId4"/>
     <sheet name="T_Cantidad" sheetId="15" r:id="rId5"/>
     <sheet name="Mes" sheetId="10" r:id="rId6"/>
@@ -227,7 +228,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,6 +248,30 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF595959"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -293,7 +318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -314,11 +339,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="21">
     <dxf>
       <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
     </dxf>
@@ -399,6 +428,16 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4466,6 +4505,76 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámicaInteranual" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A5:C8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
+      <items count="14">
+        <item x="0" h="1"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="7"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Gasto" fld="6" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A4:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
@@ -21730,6 +21839,924 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P41"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="16" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interanual: el mismo mes en distintos años</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compara cada mes con el mismo mes de otros años, separando la estacionalidad (p. ej. diciembre siempre es más caro) de la tendencia real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ojo: el primer y el último año de la serie (y el mes en curso) suelen estar incompletos; por eso el total interanual solo compara los meses con datos en los dos años.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gasto por mes y año</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Etiquetas de fila</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">% de variación frente al mismo mes del año anterior (rojo: gastas más; verde: gastas menos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mes</t>
+        </is>
+      </c>
+      <c r="B25" s="15">
+        <f>IF(OR(B$6="",ISERROR(VALUE(B$6))),"",B$6)</f>
+      </c>
+      <c r="C25" s="15">
+        <f>IF(OR(C$6="",ISERROR(VALUE(C$6))),"",C$6)</f>
+      </c>
+      <c r="D25" s="15">
+        <f>IF(OR(D$6="",ISERROR(VALUE(D$6))),"",D$6)</f>
+      </c>
+      <c r="E25" s="15">
+        <f>IF(OR(E$6="",ISERROR(VALUE(E$6))),"",E$6)</f>
+      </c>
+      <c r="F25" s="15">
+        <f>IF(OR(F$6="",ISERROR(VALUE(F$6))),"",F$6)</f>
+      </c>
+      <c r="G25" s="15">
+        <f>IF(OR(G$6="",ISERROR(VALUE(G$6))),"",G$6)</f>
+      </c>
+      <c r="H25" s="15">
+        <f>IF(OR(H$6="",ISERROR(VALUE(H$6))),"",H$6)</f>
+      </c>
+      <c r="I25" s="15">
+        <f>IF(OR(I$6="",ISERROR(VALUE(I$6))),"",I$6)</f>
+      </c>
+      <c r="J25" s="15">
+        <f>IF(OR(J$6="",ISERROR(VALUE(J$6))),"",J$6)</f>
+      </c>
+      <c r="K25" s="15">
+        <f>IF(OR(K$6="",ISERROR(VALUE(K$6))),"",K$6)</f>
+      </c>
+      <c r="L25" s="15">
+        <f>IF(OR(L$6="",ISERROR(VALUE(L$6))),"",L$6)</f>
+      </c>
+      <c r="M25" s="15">
+        <f>IF(OR(M$6="",ISERROR(VALUE(M$6))),"",M$6)</f>
+      </c>
+      <c r="N25" s="15">
+        <f>IF(OR(N$6="",ISERROR(VALUE(N$6))),"",N$6)</f>
+      </c>
+      <c r="O25" s="15">
+        <f>IF(OR(O$6="",ISERROR(VALUE(O$6))),"",O$6)</f>
+      </c>
+      <c r="P25" s="15">
+        <f>IF(OR(P$6="",ISERROR(VALUE(P$6))),"",P$6)</f>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <f>IF(OR(A7="",A8=""),"",A7)</f>
+      </c>
+      <c r="B26" s="17">
+        <f>IF(OR(B$25="",$A26="",NOT(ISNUMBER(B7)),NOT(ISNUMBER(A7)),N(A7)=0),"",B7/A7-1)</f>
+      </c>
+      <c r="C26" s="17">
+        <f>IF(OR(C$25="",$A26="",NOT(ISNUMBER(C7)),NOT(ISNUMBER(B7)),N(B7)=0),"",C7/B7-1)</f>
+      </c>
+      <c r="D26" s="17">
+        <f>IF(OR(D$25="",$A26="",NOT(ISNUMBER(D7)),NOT(ISNUMBER(C7)),N(C7)=0),"",D7/C7-1)</f>
+      </c>
+      <c r="E26" s="17">
+        <f>IF(OR(E$25="",$A26="",NOT(ISNUMBER(E7)),NOT(ISNUMBER(D7)),N(D7)=0),"",E7/D7-1)</f>
+      </c>
+      <c r="F26" s="17">
+        <f>IF(OR(F$25="",$A26="",NOT(ISNUMBER(F7)),NOT(ISNUMBER(E7)),N(E7)=0),"",F7/E7-1)</f>
+      </c>
+      <c r="G26" s="17">
+        <f>IF(OR(G$25="",$A26="",NOT(ISNUMBER(G7)),NOT(ISNUMBER(F7)),N(F7)=0),"",G7/F7-1)</f>
+      </c>
+      <c r="H26" s="17">
+        <f>IF(OR(H$25="",$A26="",NOT(ISNUMBER(H7)),NOT(ISNUMBER(G7)),N(G7)=0),"",H7/G7-1)</f>
+      </c>
+      <c r="I26" s="17">
+        <f>IF(OR(I$25="",$A26="",NOT(ISNUMBER(I7)),NOT(ISNUMBER(H7)),N(H7)=0),"",I7/H7-1)</f>
+      </c>
+      <c r="J26" s="17">
+        <f>IF(OR(J$25="",$A26="",NOT(ISNUMBER(J7)),NOT(ISNUMBER(I7)),N(I7)=0),"",J7/I7-1)</f>
+      </c>
+      <c r="K26" s="17">
+        <f>IF(OR(K$25="",$A26="",NOT(ISNUMBER(K7)),NOT(ISNUMBER(J7)),N(J7)=0),"",K7/J7-1)</f>
+      </c>
+      <c r="L26" s="17">
+        <f>IF(OR(L$25="",$A26="",NOT(ISNUMBER(L7)),NOT(ISNUMBER(K7)),N(K7)=0),"",L7/K7-1)</f>
+      </c>
+      <c r="M26" s="17">
+        <f>IF(OR(M$25="",$A26="",NOT(ISNUMBER(M7)),NOT(ISNUMBER(L7)),N(L7)=0),"",M7/L7-1)</f>
+      </c>
+      <c r="N26" s="17">
+        <f>IF(OR(N$25="",$A26="",NOT(ISNUMBER(N7)),NOT(ISNUMBER(M7)),N(M7)=0),"",N7/M7-1)</f>
+      </c>
+      <c r="O26" s="17">
+        <f>IF(OR(O$25="",$A26="",NOT(ISNUMBER(O7)),NOT(ISNUMBER(N7)),N(N7)=0),"",O7/N7-1)</f>
+      </c>
+      <c r="P26" s="17">
+        <f>IF(OR(P$25="",$A26="",NOT(ISNUMBER(P7)),NOT(ISNUMBER(O7)),N(O7)=0),"",P7/O7-1)</f>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <f>IF(OR(A8="",A9=""),"",A8)</f>
+      </c>
+      <c r="B27" s="17">
+        <f>IF(OR(B$25="",$A27="",NOT(ISNUMBER(B8)),NOT(ISNUMBER(A8)),N(A8)=0),"",B8/A8-1)</f>
+      </c>
+      <c r="C27" s="17">
+        <f>IF(OR(C$25="",$A27="",NOT(ISNUMBER(C8)),NOT(ISNUMBER(B8)),N(B8)=0),"",C8/B8-1)</f>
+      </c>
+      <c r="D27" s="17">
+        <f>IF(OR(D$25="",$A27="",NOT(ISNUMBER(D8)),NOT(ISNUMBER(C8)),N(C8)=0),"",D8/C8-1)</f>
+      </c>
+      <c r="E27" s="17">
+        <f>IF(OR(E$25="",$A27="",NOT(ISNUMBER(E8)),NOT(ISNUMBER(D8)),N(D8)=0),"",E8/D8-1)</f>
+      </c>
+      <c r="F27" s="17">
+        <f>IF(OR(F$25="",$A27="",NOT(ISNUMBER(F8)),NOT(ISNUMBER(E8)),N(E8)=0),"",F8/E8-1)</f>
+      </c>
+      <c r="G27" s="17">
+        <f>IF(OR(G$25="",$A27="",NOT(ISNUMBER(G8)),NOT(ISNUMBER(F8)),N(F8)=0),"",G8/F8-1)</f>
+      </c>
+      <c r="H27" s="17">
+        <f>IF(OR(H$25="",$A27="",NOT(ISNUMBER(H8)),NOT(ISNUMBER(G8)),N(G8)=0),"",H8/G8-1)</f>
+      </c>
+      <c r="I27" s="17">
+        <f>IF(OR(I$25="",$A27="",NOT(ISNUMBER(I8)),NOT(ISNUMBER(H8)),N(H8)=0),"",I8/H8-1)</f>
+      </c>
+      <c r="J27" s="17">
+        <f>IF(OR(J$25="",$A27="",NOT(ISNUMBER(J8)),NOT(ISNUMBER(I8)),N(I8)=0),"",J8/I8-1)</f>
+      </c>
+      <c r="K27" s="17">
+        <f>IF(OR(K$25="",$A27="",NOT(ISNUMBER(K8)),NOT(ISNUMBER(J8)),N(J8)=0),"",K8/J8-1)</f>
+      </c>
+      <c r="L27" s="17">
+        <f>IF(OR(L$25="",$A27="",NOT(ISNUMBER(L8)),NOT(ISNUMBER(K8)),N(K8)=0),"",L8/K8-1)</f>
+      </c>
+      <c r="M27" s="17">
+        <f>IF(OR(M$25="",$A27="",NOT(ISNUMBER(M8)),NOT(ISNUMBER(L8)),N(L8)=0),"",M8/L8-1)</f>
+      </c>
+      <c r="N27" s="17">
+        <f>IF(OR(N$25="",$A27="",NOT(ISNUMBER(N8)),NOT(ISNUMBER(M8)),N(M8)=0),"",N8/M8-1)</f>
+      </c>
+      <c r="O27" s="17">
+        <f>IF(OR(O$25="",$A27="",NOT(ISNUMBER(O8)),NOT(ISNUMBER(N8)),N(N8)=0),"",O8/N8-1)</f>
+      </c>
+      <c r="P27" s="17">
+        <f>IF(OR(P$25="",$A27="",NOT(ISNUMBER(P8)),NOT(ISNUMBER(O8)),N(O8)=0),"",P8/O8-1)</f>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <f>IF(OR(A9="",A10=""),"",A9)</f>
+      </c>
+      <c r="B28" s="17">
+        <f>IF(OR(B$25="",$A28="",NOT(ISNUMBER(B9)),NOT(ISNUMBER(A9)),N(A9)=0),"",B9/A9-1)</f>
+      </c>
+      <c r="C28" s="17">
+        <f>IF(OR(C$25="",$A28="",NOT(ISNUMBER(C9)),NOT(ISNUMBER(B9)),N(B9)=0),"",C9/B9-1)</f>
+      </c>
+      <c r="D28" s="17">
+        <f>IF(OR(D$25="",$A28="",NOT(ISNUMBER(D9)),NOT(ISNUMBER(C9)),N(C9)=0),"",D9/C9-1)</f>
+      </c>
+      <c r="E28" s="17">
+        <f>IF(OR(E$25="",$A28="",NOT(ISNUMBER(E9)),NOT(ISNUMBER(D9)),N(D9)=0),"",E9/D9-1)</f>
+      </c>
+      <c r="F28" s="17">
+        <f>IF(OR(F$25="",$A28="",NOT(ISNUMBER(F9)),NOT(ISNUMBER(E9)),N(E9)=0),"",F9/E9-1)</f>
+      </c>
+      <c r="G28" s="17">
+        <f>IF(OR(G$25="",$A28="",NOT(ISNUMBER(G9)),NOT(ISNUMBER(F9)),N(F9)=0),"",G9/F9-1)</f>
+      </c>
+      <c r="H28" s="17">
+        <f>IF(OR(H$25="",$A28="",NOT(ISNUMBER(H9)),NOT(ISNUMBER(G9)),N(G9)=0),"",H9/G9-1)</f>
+      </c>
+      <c r="I28" s="17">
+        <f>IF(OR(I$25="",$A28="",NOT(ISNUMBER(I9)),NOT(ISNUMBER(H9)),N(H9)=0),"",I9/H9-1)</f>
+      </c>
+      <c r="J28" s="17">
+        <f>IF(OR(J$25="",$A28="",NOT(ISNUMBER(J9)),NOT(ISNUMBER(I9)),N(I9)=0),"",J9/I9-1)</f>
+      </c>
+      <c r="K28" s="17">
+        <f>IF(OR(K$25="",$A28="",NOT(ISNUMBER(K9)),NOT(ISNUMBER(J9)),N(J9)=0),"",K9/J9-1)</f>
+      </c>
+      <c r="L28" s="17">
+        <f>IF(OR(L$25="",$A28="",NOT(ISNUMBER(L9)),NOT(ISNUMBER(K9)),N(K9)=0),"",L9/K9-1)</f>
+      </c>
+      <c r="M28" s="17">
+        <f>IF(OR(M$25="",$A28="",NOT(ISNUMBER(M9)),NOT(ISNUMBER(L9)),N(L9)=0),"",M9/L9-1)</f>
+      </c>
+      <c r="N28" s="17">
+        <f>IF(OR(N$25="",$A28="",NOT(ISNUMBER(N9)),NOT(ISNUMBER(M9)),N(M9)=0),"",N9/M9-1)</f>
+      </c>
+      <c r="O28" s="17">
+        <f>IF(OR(O$25="",$A28="",NOT(ISNUMBER(O9)),NOT(ISNUMBER(N9)),N(N9)=0),"",O9/N9-1)</f>
+      </c>
+      <c r="P28" s="17">
+        <f>IF(OR(P$25="",$A28="",NOT(ISNUMBER(P9)),NOT(ISNUMBER(O9)),N(O9)=0),"",P9/O9-1)</f>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <f>IF(OR(A10="",A11=""),"",A10)</f>
+      </c>
+      <c r="B29" s="17">
+        <f>IF(OR(B$25="",$A29="",NOT(ISNUMBER(B10)),NOT(ISNUMBER(A10)),N(A10)=0),"",B10/A10-1)</f>
+      </c>
+      <c r="C29" s="17">
+        <f>IF(OR(C$25="",$A29="",NOT(ISNUMBER(C10)),NOT(ISNUMBER(B10)),N(B10)=0),"",C10/B10-1)</f>
+      </c>
+      <c r="D29" s="17">
+        <f>IF(OR(D$25="",$A29="",NOT(ISNUMBER(D10)),NOT(ISNUMBER(C10)),N(C10)=0),"",D10/C10-1)</f>
+      </c>
+      <c r="E29" s="17">
+        <f>IF(OR(E$25="",$A29="",NOT(ISNUMBER(E10)),NOT(ISNUMBER(D10)),N(D10)=0),"",E10/D10-1)</f>
+      </c>
+      <c r="F29" s="17">
+        <f>IF(OR(F$25="",$A29="",NOT(ISNUMBER(F10)),NOT(ISNUMBER(E10)),N(E10)=0),"",F10/E10-1)</f>
+      </c>
+      <c r="G29" s="17">
+        <f>IF(OR(G$25="",$A29="",NOT(ISNUMBER(G10)),NOT(ISNUMBER(F10)),N(F10)=0),"",G10/F10-1)</f>
+      </c>
+      <c r="H29" s="17">
+        <f>IF(OR(H$25="",$A29="",NOT(ISNUMBER(H10)),NOT(ISNUMBER(G10)),N(G10)=0),"",H10/G10-1)</f>
+      </c>
+      <c r="I29" s="17">
+        <f>IF(OR(I$25="",$A29="",NOT(ISNUMBER(I10)),NOT(ISNUMBER(H10)),N(H10)=0),"",I10/H10-1)</f>
+      </c>
+      <c r="J29" s="17">
+        <f>IF(OR(J$25="",$A29="",NOT(ISNUMBER(J10)),NOT(ISNUMBER(I10)),N(I10)=0),"",J10/I10-1)</f>
+      </c>
+      <c r="K29" s="17">
+        <f>IF(OR(K$25="",$A29="",NOT(ISNUMBER(K10)),NOT(ISNUMBER(J10)),N(J10)=0),"",K10/J10-1)</f>
+      </c>
+      <c r="L29" s="17">
+        <f>IF(OR(L$25="",$A29="",NOT(ISNUMBER(L10)),NOT(ISNUMBER(K10)),N(K10)=0),"",L10/K10-1)</f>
+      </c>
+      <c r="M29" s="17">
+        <f>IF(OR(M$25="",$A29="",NOT(ISNUMBER(M10)),NOT(ISNUMBER(L10)),N(L10)=0),"",M10/L10-1)</f>
+      </c>
+      <c r="N29" s="17">
+        <f>IF(OR(N$25="",$A29="",NOT(ISNUMBER(N10)),NOT(ISNUMBER(M10)),N(M10)=0),"",N10/M10-1)</f>
+      </c>
+      <c r="O29" s="17">
+        <f>IF(OR(O$25="",$A29="",NOT(ISNUMBER(O10)),NOT(ISNUMBER(N10)),N(N10)=0),"",O10/N10-1)</f>
+      </c>
+      <c r="P29" s="17">
+        <f>IF(OR(P$25="",$A29="",NOT(ISNUMBER(P10)),NOT(ISNUMBER(O10)),N(O10)=0),"",P10/O10-1)</f>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <f>IF(OR(A11="",A12=""),"",A11)</f>
+      </c>
+      <c r="B30" s="17">
+        <f>IF(OR(B$25="",$A30="",NOT(ISNUMBER(B11)),NOT(ISNUMBER(A11)),N(A11)=0),"",B11/A11-1)</f>
+      </c>
+      <c r="C30" s="17">
+        <f>IF(OR(C$25="",$A30="",NOT(ISNUMBER(C11)),NOT(ISNUMBER(B11)),N(B11)=0),"",C11/B11-1)</f>
+      </c>
+      <c r="D30" s="17">
+        <f>IF(OR(D$25="",$A30="",NOT(ISNUMBER(D11)),NOT(ISNUMBER(C11)),N(C11)=0),"",D11/C11-1)</f>
+      </c>
+      <c r="E30" s="17">
+        <f>IF(OR(E$25="",$A30="",NOT(ISNUMBER(E11)),NOT(ISNUMBER(D11)),N(D11)=0),"",E11/D11-1)</f>
+      </c>
+      <c r="F30" s="17">
+        <f>IF(OR(F$25="",$A30="",NOT(ISNUMBER(F11)),NOT(ISNUMBER(E11)),N(E11)=0),"",F11/E11-1)</f>
+      </c>
+      <c r="G30" s="17">
+        <f>IF(OR(G$25="",$A30="",NOT(ISNUMBER(G11)),NOT(ISNUMBER(F11)),N(F11)=0),"",G11/F11-1)</f>
+      </c>
+      <c r="H30" s="17">
+        <f>IF(OR(H$25="",$A30="",NOT(ISNUMBER(H11)),NOT(ISNUMBER(G11)),N(G11)=0),"",H11/G11-1)</f>
+      </c>
+      <c r="I30" s="17">
+        <f>IF(OR(I$25="",$A30="",NOT(ISNUMBER(I11)),NOT(ISNUMBER(H11)),N(H11)=0),"",I11/H11-1)</f>
+      </c>
+      <c r="J30" s="17">
+        <f>IF(OR(J$25="",$A30="",NOT(ISNUMBER(J11)),NOT(ISNUMBER(I11)),N(I11)=0),"",J11/I11-1)</f>
+      </c>
+      <c r="K30" s="17">
+        <f>IF(OR(K$25="",$A30="",NOT(ISNUMBER(K11)),NOT(ISNUMBER(J11)),N(J11)=0),"",K11/J11-1)</f>
+      </c>
+      <c r="L30" s="17">
+        <f>IF(OR(L$25="",$A30="",NOT(ISNUMBER(L11)),NOT(ISNUMBER(K11)),N(K11)=0),"",L11/K11-1)</f>
+      </c>
+      <c r="M30" s="17">
+        <f>IF(OR(M$25="",$A30="",NOT(ISNUMBER(M11)),NOT(ISNUMBER(L11)),N(L11)=0),"",M11/L11-1)</f>
+      </c>
+      <c r="N30" s="17">
+        <f>IF(OR(N$25="",$A30="",NOT(ISNUMBER(N11)),NOT(ISNUMBER(M11)),N(M11)=0),"",N11/M11-1)</f>
+      </c>
+      <c r="O30" s="17">
+        <f>IF(OR(O$25="",$A30="",NOT(ISNUMBER(O11)),NOT(ISNUMBER(N11)),N(N11)=0),"",O11/N11-1)</f>
+      </c>
+      <c r="P30" s="17">
+        <f>IF(OR(P$25="",$A30="",NOT(ISNUMBER(P11)),NOT(ISNUMBER(O11)),N(O11)=0),"",P11/O11-1)</f>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <f>IF(OR(A12="",A13=""),"",A12)</f>
+      </c>
+      <c r="B31" s="17">
+        <f>IF(OR(B$25="",$A31="",NOT(ISNUMBER(B12)),NOT(ISNUMBER(A12)),N(A12)=0),"",B12/A12-1)</f>
+      </c>
+      <c r="C31" s="17">
+        <f>IF(OR(C$25="",$A31="",NOT(ISNUMBER(C12)),NOT(ISNUMBER(B12)),N(B12)=0),"",C12/B12-1)</f>
+      </c>
+      <c r="D31" s="17">
+        <f>IF(OR(D$25="",$A31="",NOT(ISNUMBER(D12)),NOT(ISNUMBER(C12)),N(C12)=0),"",D12/C12-1)</f>
+      </c>
+      <c r="E31" s="17">
+        <f>IF(OR(E$25="",$A31="",NOT(ISNUMBER(E12)),NOT(ISNUMBER(D12)),N(D12)=0),"",E12/D12-1)</f>
+      </c>
+      <c r="F31" s="17">
+        <f>IF(OR(F$25="",$A31="",NOT(ISNUMBER(F12)),NOT(ISNUMBER(E12)),N(E12)=0),"",F12/E12-1)</f>
+      </c>
+      <c r="G31" s="17">
+        <f>IF(OR(G$25="",$A31="",NOT(ISNUMBER(G12)),NOT(ISNUMBER(F12)),N(F12)=0),"",G12/F12-1)</f>
+      </c>
+      <c r="H31" s="17">
+        <f>IF(OR(H$25="",$A31="",NOT(ISNUMBER(H12)),NOT(ISNUMBER(G12)),N(G12)=0),"",H12/G12-1)</f>
+      </c>
+      <c r="I31" s="17">
+        <f>IF(OR(I$25="",$A31="",NOT(ISNUMBER(I12)),NOT(ISNUMBER(H12)),N(H12)=0),"",I12/H12-1)</f>
+      </c>
+      <c r="J31" s="17">
+        <f>IF(OR(J$25="",$A31="",NOT(ISNUMBER(J12)),NOT(ISNUMBER(I12)),N(I12)=0),"",J12/I12-1)</f>
+      </c>
+      <c r="K31" s="17">
+        <f>IF(OR(K$25="",$A31="",NOT(ISNUMBER(K12)),NOT(ISNUMBER(J12)),N(J12)=0),"",K12/J12-1)</f>
+      </c>
+      <c r="L31" s="17">
+        <f>IF(OR(L$25="",$A31="",NOT(ISNUMBER(L12)),NOT(ISNUMBER(K12)),N(K12)=0),"",L12/K12-1)</f>
+      </c>
+      <c r="M31" s="17">
+        <f>IF(OR(M$25="",$A31="",NOT(ISNUMBER(M12)),NOT(ISNUMBER(L12)),N(L12)=0),"",M12/L12-1)</f>
+      </c>
+      <c r="N31" s="17">
+        <f>IF(OR(N$25="",$A31="",NOT(ISNUMBER(N12)),NOT(ISNUMBER(M12)),N(M12)=0),"",N12/M12-1)</f>
+      </c>
+      <c r="O31" s="17">
+        <f>IF(OR(O$25="",$A31="",NOT(ISNUMBER(O12)),NOT(ISNUMBER(N12)),N(N12)=0),"",O12/N12-1)</f>
+      </c>
+      <c r="P31" s="17">
+        <f>IF(OR(P$25="",$A31="",NOT(ISNUMBER(P12)),NOT(ISNUMBER(O12)),N(O12)=0),"",P12/O12-1)</f>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <f>IF(OR(A13="",A14=""),"",A13)</f>
+      </c>
+      <c r="B32" s="17">
+        <f>IF(OR(B$25="",$A32="",NOT(ISNUMBER(B13)),NOT(ISNUMBER(A13)),N(A13)=0),"",B13/A13-1)</f>
+      </c>
+      <c r="C32" s="17">
+        <f>IF(OR(C$25="",$A32="",NOT(ISNUMBER(C13)),NOT(ISNUMBER(B13)),N(B13)=0),"",C13/B13-1)</f>
+      </c>
+      <c r="D32" s="17">
+        <f>IF(OR(D$25="",$A32="",NOT(ISNUMBER(D13)),NOT(ISNUMBER(C13)),N(C13)=0),"",D13/C13-1)</f>
+      </c>
+      <c r="E32" s="17">
+        <f>IF(OR(E$25="",$A32="",NOT(ISNUMBER(E13)),NOT(ISNUMBER(D13)),N(D13)=0),"",E13/D13-1)</f>
+      </c>
+      <c r="F32" s="17">
+        <f>IF(OR(F$25="",$A32="",NOT(ISNUMBER(F13)),NOT(ISNUMBER(E13)),N(E13)=0),"",F13/E13-1)</f>
+      </c>
+      <c r="G32" s="17">
+        <f>IF(OR(G$25="",$A32="",NOT(ISNUMBER(G13)),NOT(ISNUMBER(F13)),N(F13)=0),"",G13/F13-1)</f>
+      </c>
+      <c r="H32" s="17">
+        <f>IF(OR(H$25="",$A32="",NOT(ISNUMBER(H13)),NOT(ISNUMBER(G13)),N(G13)=0),"",H13/G13-1)</f>
+      </c>
+      <c r="I32" s="17">
+        <f>IF(OR(I$25="",$A32="",NOT(ISNUMBER(I13)),NOT(ISNUMBER(H13)),N(H13)=0),"",I13/H13-1)</f>
+      </c>
+      <c r="J32" s="17">
+        <f>IF(OR(J$25="",$A32="",NOT(ISNUMBER(J13)),NOT(ISNUMBER(I13)),N(I13)=0),"",J13/I13-1)</f>
+      </c>
+      <c r="K32" s="17">
+        <f>IF(OR(K$25="",$A32="",NOT(ISNUMBER(K13)),NOT(ISNUMBER(J13)),N(J13)=0),"",K13/J13-1)</f>
+      </c>
+      <c r="L32" s="17">
+        <f>IF(OR(L$25="",$A32="",NOT(ISNUMBER(L13)),NOT(ISNUMBER(K13)),N(K13)=0),"",L13/K13-1)</f>
+      </c>
+      <c r="M32" s="17">
+        <f>IF(OR(M$25="",$A32="",NOT(ISNUMBER(M13)),NOT(ISNUMBER(L13)),N(L13)=0),"",M13/L13-1)</f>
+      </c>
+      <c r="N32" s="17">
+        <f>IF(OR(N$25="",$A32="",NOT(ISNUMBER(N13)),NOT(ISNUMBER(M13)),N(M13)=0),"",N13/M13-1)</f>
+      </c>
+      <c r="O32" s="17">
+        <f>IF(OR(O$25="",$A32="",NOT(ISNUMBER(O13)),NOT(ISNUMBER(N13)),N(N13)=0),"",O13/N13-1)</f>
+      </c>
+      <c r="P32" s="17">
+        <f>IF(OR(P$25="",$A32="",NOT(ISNUMBER(P13)),NOT(ISNUMBER(O13)),N(O13)=0),"",P13/O13-1)</f>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <f>IF(OR(A14="",A15=""),"",A14)</f>
+      </c>
+      <c r="B33" s="17">
+        <f>IF(OR(B$25="",$A33="",NOT(ISNUMBER(B14)),NOT(ISNUMBER(A14)),N(A14)=0),"",B14/A14-1)</f>
+      </c>
+      <c r="C33" s="17">
+        <f>IF(OR(C$25="",$A33="",NOT(ISNUMBER(C14)),NOT(ISNUMBER(B14)),N(B14)=0),"",C14/B14-1)</f>
+      </c>
+      <c r="D33" s="17">
+        <f>IF(OR(D$25="",$A33="",NOT(ISNUMBER(D14)),NOT(ISNUMBER(C14)),N(C14)=0),"",D14/C14-1)</f>
+      </c>
+      <c r="E33" s="17">
+        <f>IF(OR(E$25="",$A33="",NOT(ISNUMBER(E14)),NOT(ISNUMBER(D14)),N(D14)=0),"",E14/D14-1)</f>
+      </c>
+      <c r="F33" s="17">
+        <f>IF(OR(F$25="",$A33="",NOT(ISNUMBER(F14)),NOT(ISNUMBER(E14)),N(E14)=0),"",F14/E14-1)</f>
+      </c>
+      <c r="G33" s="17">
+        <f>IF(OR(G$25="",$A33="",NOT(ISNUMBER(G14)),NOT(ISNUMBER(F14)),N(F14)=0),"",G14/F14-1)</f>
+      </c>
+      <c r="H33" s="17">
+        <f>IF(OR(H$25="",$A33="",NOT(ISNUMBER(H14)),NOT(ISNUMBER(G14)),N(G14)=0),"",H14/G14-1)</f>
+      </c>
+      <c r="I33" s="17">
+        <f>IF(OR(I$25="",$A33="",NOT(ISNUMBER(I14)),NOT(ISNUMBER(H14)),N(H14)=0),"",I14/H14-1)</f>
+      </c>
+      <c r="J33" s="17">
+        <f>IF(OR(J$25="",$A33="",NOT(ISNUMBER(J14)),NOT(ISNUMBER(I14)),N(I14)=0),"",J14/I14-1)</f>
+      </c>
+      <c r="K33" s="17">
+        <f>IF(OR(K$25="",$A33="",NOT(ISNUMBER(K14)),NOT(ISNUMBER(J14)),N(J14)=0),"",K14/J14-1)</f>
+      </c>
+      <c r="L33" s="17">
+        <f>IF(OR(L$25="",$A33="",NOT(ISNUMBER(L14)),NOT(ISNUMBER(K14)),N(K14)=0),"",L14/K14-1)</f>
+      </c>
+      <c r="M33" s="17">
+        <f>IF(OR(M$25="",$A33="",NOT(ISNUMBER(M14)),NOT(ISNUMBER(L14)),N(L14)=0),"",M14/L14-1)</f>
+      </c>
+      <c r="N33" s="17">
+        <f>IF(OR(N$25="",$A33="",NOT(ISNUMBER(N14)),NOT(ISNUMBER(M14)),N(M14)=0),"",N14/M14-1)</f>
+      </c>
+      <c r="O33" s="17">
+        <f>IF(OR(O$25="",$A33="",NOT(ISNUMBER(O14)),NOT(ISNUMBER(N14)),N(N14)=0),"",O14/N14-1)</f>
+      </c>
+      <c r="P33" s="17">
+        <f>IF(OR(P$25="",$A33="",NOT(ISNUMBER(P14)),NOT(ISNUMBER(O14)),N(O14)=0),"",P14/O14-1)</f>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <f>IF(OR(A15="",A16=""),"",A15)</f>
+      </c>
+      <c r="B34" s="17">
+        <f>IF(OR(B$25="",$A34="",NOT(ISNUMBER(B15)),NOT(ISNUMBER(A15)),N(A15)=0),"",B15/A15-1)</f>
+      </c>
+      <c r="C34" s="17">
+        <f>IF(OR(C$25="",$A34="",NOT(ISNUMBER(C15)),NOT(ISNUMBER(B15)),N(B15)=0),"",C15/B15-1)</f>
+      </c>
+      <c r="D34" s="17">
+        <f>IF(OR(D$25="",$A34="",NOT(ISNUMBER(D15)),NOT(ISNUMBER(C15)),N(C15)=0),"",D15/C15-1)</f>
+      </c>
+      <c r="E34" s="17">
+        <f>IF(OR(E$25="",$A34="",NOT(ISNUMBER(E15)),NOT(ISNUMBER(D15)),N(D15)=0),"",E15/D15-1)</f>
+      </c>
+      <c r="F34" s="17">
+        <f>IF(OR(F$25="",$A34="",NOT(ISNUMBER(F15)),NOT(ISNUMBER(E15)),N(E15)=0),"",F15/E15-1)</f>
+      </c>
+      <c r="G34" s="17">
+        <f>IF(OR(G$25="",$A34="",NOT(ISNUMBER(G15)),NOT(ISNUMBER(F15)),N(F15)=0),"",G15/F15-1)</f>
+      </c>
+      <c r="H34" s="17">
+        <f>IF(OR(H$25="",$A34="",NOT(ISNUMBER(H15)),NOT(ISNUMBER(G15)),N(G15)=0),"",H15/G15-1)</f>
+      </c>
+      <c r="I34" s="17">
+        <f>IF(OR(I$25="",$A34="",NOT(ISNUMBER(I15)),NOT(ISNUMBER(H15)),N(H15)=0),"",I15/H15-1)</f>
+      </c>
+      <c r="J34" s="17">
+        <f>IF(OR(J$25="",$A34="",NOT(ISNUMBER(J15)),NOT(ISNUMBER(I15)),N(I15)=0),"",J15/I15-1)</f>
+      </c>
+      <c r="K34" s="17">
+        <f>IF(OR(K$25="",$A34="",NOT(ISNUMBER(K15)),NOT(ISNUMBER(J15)),N(J15)=0),"",K15/J15-1)</f>
+      </c>
+      <c r="L34" s="17">
+        <f>IF(OR(L$25="",$A34="",NOT(ISNUMBER(L15)),NOT(ISNUMBER(K15)),N(K15)=0),"",L15/K15-1)</f>
+      </c>
+      <c r="M34" s="17">
+        <f>IF(OR(M$25="",$A34="",NOT(ISNUMBER(M15)),NOT(ISNUMBER(L15)),N(L15)=0),"",M15/L15-1)</f>
+      </c>
+      <c r="N34" s="17">
+        <f>IF(OR(N$25="",$A34="",NOT(ISNUMBER(N15)),NOT(ISNUMBER(M15)),N(M15)=0),"",N15/M15-1)</f>
+      </c>
+      <c r="O34" s="17">
+        <f>IF(OR(O$25="",$A34="",NOT(ISNUMBER(O15)),NOT(ISNUMBER(N15)),N(N15)=0),"",O15/N15-1)</f>
+      </c>
+      <c r="P34" s="17">
+        <f>IF(OR(P$25="",$A34="",NOT(ISNUMBER(P15)),NOT(ISNUMBER(O15)),N(O15)=0),"",P15/O15-1)</f>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <f>IF(OR(A16="",A17=""),"",A16)</f>
+      </c>
+      <c r="B35" s="17">
+        <f>IF(OR(B$25="",$A35="",NOT(ISNUMBER(B16)),NOT(ISNUMBER(A16)),N(A16)=0),"",B16/A16-1)</f>
+      </c>
+      <c r="C35" s="17">
+        <f>IF(OR(C$25="",$A35="",NOT(ISNUMBER(C16)),NOT(ISNUMBER(B16)),N(B16)=0),"",C16/B16-1)</f>
+      </c>
+      <c r="D35" s="17">
+        <f>IF(OR(D$25="",$A35="",NOT(ISNUMBER(D16)),NOT(ISNUMBER(C16)),N(C16)=0),"",D16/C16-1)</f>
+      </c>
+      <c r="E35" s="17">
+        <f>IF(OR(E$25="",$A35="",NOT(ISNUMBER(E16)),NOT(ISNUMBER(D16)),N(D16)=0),"",E16/D16-1)</f>
+      </c>
+      <c r="F35" s="17">
+        <f>IF(OR(F$25="",$A35="",NOT(ISNUMBER(F16)),NOT(ISNUMBER(E16)),N(E16)=0),"",F16/E16-1)</f>
+      </c>
+      <c r="G35" s="17">
+        <f>IF(OR(G$25="",$A35="",NOT(ISNUMBER(G16)),NOT(ISNUMBER(F16)),N(F16)=0),"",G16/F16-1)</f>
+      </c>
+      <c r="H35" s="17">
+        <f>IF(OR(H$25="",$A35="",NOT(ISNUMBER(H16)),NOT(ISNUMBER(G16)),N(G16)=0),"",H16/G16-1)</f>
+      </c>
+      <c r="I35" s="17">
+        <f>IF(OR(I$25="",$A35="",NOT(ISNUMBER(I16)),NOT(ISNUMBER(H16)),N(H16)=0),"",I16/H16-1)</f>
+      </c>
+      <c r="J35" s="17">
+        <f>IF(OR(J$25="",$A35="",NOT(ISNUMBER(J16)),NOT(ISNUMBER(I16)),N(I16)=0),"",J16/I16-1)</f>
+      </c>
+      <c r="K35" s="17">
+        <f>IF(OR(K$25="",$A35="",NOT(ISNUMBER(K16)),NOT(ISNUMBER(J16)),N(J16)=0),"",K16/J16-1)</f>
+      </c>
+      <c r="L35" s="17">
+        <f>IF(OR(L$25="",$A35="",NOT(ISNUMBER(L16)),NOT(ISNUMBER(K16)),N(K16)=0),"",L16/K16-1)</f>
+      </c>
+      <c r="M35" s="17">
+        <f>IF(OR(M$25="",$A35="",NOT(ISNUMBER(M16)),NOT(ISNUMBER(L16)),N(L16)=0),"",M16/L16-1)</f>
+      </c>
+      <c r="N35" s="17">
+        <f>IF(OR(N$25="",$A35="",NOT(ISNUMBER(N16)),NOT(ISNUMBER(M16)),N(M16)=0),"",N16/M16-1)</f>
+      </c>
+      <c r="O35" s="17">
+        <f>IF(OR(O$25="",$A35="",NOT(ISNUMBER(O16)),NOT(ISNUMBER(N16)),N(N16)=0),"",O16/N16-1)</f>
+      </c>
+      <c r="P35" s="17">
+        <f>IF(OR(P$25="",$A35="",NOT(ISNUMBER(P16)),NOT(ISNUMBER(O16)),N(O16)=0),"",P16/O16-1)</f>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <f>IF(OR(A17="",A18=""),"",A17)</f>
+      </c>
+      <c r="B36" s="17">
+        <f>IF(OR(B$25="",$A36="",NOT(ISNUMBER(B17)),NOT(ISNUMBER(A17)),N(A17)=0),"",B17/A17-1)</f>
+      </c>
+      <c r="C36" s="17">
+        <f>IF(OR(C$25="",$A36="",NOT(ISNUMBER(C17)),NOT(ISNUMBER(B17)),N(B17)=0),"",C17/B17-1)</f>
+      </c>
+      <c r="D36" s="17">
+        <f>IF(OR(D$25="",$A36="",NOT(ISNUMBER(D17)),NOT(ISNUMBER(C17)),N(C17)=0),"",D17/C17-1)</f>
+      </c>
+      <c r="E36" s="17">
+        <f>IF(OR(E$25="",$A36="",NOT(ISNUMBER(E17)),NOT(ISNUMBER(D17)),N(D17)=0),"",E17/D17-1)</f>
+      </c>
+      <c r="F36" s="17">
+        <f>IF(OR(F$25="",$A36="",NOT(ISNUMBER(F17)),NOT(ISNUMBER(E17)),N(E17)=0),"",F17/E17-1)</f>
+      </c>
+      <c r="G36" s="17">
+        <f>IF(OR(G$25="",$A36="",NOT(ISNUMBER(G17)),NOT(ISNUMBER(F17)),N(F17)=0),"",G17/F17-1)</f>
+      </c>
+      <c r="H36" s="17">
+        <f>IF(OR(H$25="",$A36="",NOT(ISNUMBER(H17)),NOT(ISNUMBER(G17)),N(G17)=0),"",H17/G17-1)</f>
+      </c>
+      <c r="I36" s="17">
+        <f>IF(OR(I$25="",$A36="",NOT(ISNUMBER(I17)),NOT(ISNUMBER(H17)),N(H17)=0),"",I17/H17-1)</f>
+      </c>
+      <c r="J36" s="17">
+        <f>IF(OR(J$25="",$A36="",NOT(ISNUMBER(J17)),NOT(ISNUMBER(I17)),N(I17)=0),"",J17/I17-1)</f>
+      </c>
+      <c r="K36" s="17">
+        <f>IF(OR(K$25="",$A36="",NOT(ISNUMBER(K17)),NOT(ISNUMBER(J17)),N(J17)=0),"",K17/J17-1)</f>
+      </c>
+      <c r="L36" s="17">
+        <f>IF(OR(L$25="",$A36="",NOT(ISNUMBER(L17)),NOT(ISNUMBER(K17)),N(K17)=0),"",L17/K17-1)</f>
+      </c>
+      <c r="M36" s="17">
+        <f>IF(OR(M$25="",$A36="",NOT(ISNUMBER(M17)),NOT(ISNUMBER(L17)),N(L17)=0),"",M17/L17-1)</f>
+      </c>
+      <c r="N36" s="17">
+        <f>IF(OR(N$25="",$A36="",NOT(ISNUMBER(N17)),NOT(ISNUMBER(M17)),N(M17)=0),"",N17/M17-1)</f>
+      </c>
+      <c r="O36" s="17">
+        <f>IF(OR(O$25="",$A36="",NOT(ISNUMBER(O17)),NOT(ISNUMBER(N17)),N(N17)=0),"",O17/N17-1)</f>
+      </c>
+      <c r="P36" s="17">
+        <f>IF(OR(P$25="",$A36="",NOT(ISNUMBER(P17)),NOT(ISNUMBER(O17)),N(O17)=0),"",P17/O17-1)</f>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <f>IF(OR(A18="",A19=""),"",A18)</f>
+      </c>
+      <c r="B37" s="17">
+        <f>IF(OR(B$25="",$A37="",NOT(ISNUMBER(B18)),NOT(ISNUMBER(A18)),N(A18)=0),"",B18/A18-1)</f>
+      </c>
+      <c r="C37" s="17">
+        <f>IF(OR(C$25="",$A37="",NOT(ISNUMBER(C18)),NOT(ISNUMBER(B18)),N(B18)=0),"",C18/B18-1)</f>
+      </c>
+      <c r="D37" s="17">
+        <f>IF(OR(D$25="",$A37="",NOT(ISNUMBER(D18)),NOT(ISNUMBER(C18)),N(C18)=0),"",D18/C18-1)</f>
+      </c>
+      <c r="E37" s="17">
+        <f>IF(OR(E$25="",$A37="",NOT(ISNUMBER(E18)),NOT(ISNUMBER(D18)),N(D18)=0),"",E18/D18-1)</f>
+      </c>
+      <c r="F37" s="17">
+        <f>IF(OR(F$25="",$A37="",NOT(ISNUMBER(F18)),NOT(ISNUMBER(E18)),N(E18)=0),"",F18/E18-1)</f>
+      </c>
+      <c r="G37" s="17">
+        <f>IF(OR(G$25="",$A37="",NOT(ISNUMBER(G18)),NOT(ISNUMBER(F18)),N(F18)=0),"",G18/F18-1)</f>
+      </c>
+      <c r="H37" s="17">
+        <f>IF(OR(H$25="",$A37="",NOT(ISNUMBER(H18)),NOT(ISNUMBER(G18)),N(G18)=0),"",H18/G18-1)</f>
+      </c>
+      <c r="I37" s="17">
+        <f>IF(OR(I$25="",$A37="",NOT(ISNUMBER(I18)),NOT(ISNUMBER(H18)),N(H18)=0),"",I18/H18-1)</f>
+      </c>
+      <c r="J37" s="17">
+        <f>IF(OR(J$25="",$A37="",NOT(ISNUMBER(J18)),NOT(ISNUMBER(I18)),N(I18)=0),"",J18/I18-1)</f>
+      </c>
+      <c r="K37" s="17">
+        <f>IF(OR(K$25="",$A37="",NOT(ISNUMBER(K18)),NOT(ISNUMBER(J18)),N(J18)=0),"",K18/J18-1)</f>
+      </c>
+      <c r="L37" s="17">
+        <f>IF(OR(L$25="",$A37="",NOT(ISNUMBER(L18)),NOT(ISNUMBER(K18)),N(K18)=0),"",L18/K18-1)</f>
+      </c>
+      <c r="M37" s="17">
+        <f>IF(OR(M$25="",$A37="",NOT(ISNUMBER(M18)),NOT(ISNUMBER(L18)),N(L18)=0),"",M18/L18-1)</f>
+      </c>
+      <c r="N37" s="17">
+        <f>IF(OR(N$25="",$A37="",NOT(ISNUMBER(N18)),NOT(ISNUMBER(M18)),N(M18)=0),"",N18/M18-1)</f>
+      </c>
+      <c r="O37" s="17">
+        <f>IF(OR(O$25="",$A37="",NOT(ISNUMBER(O18)),NOT(ISNUMBER(N18)),N(N18)=0),"",O18/N18-1)</f>
+      </c>
+      <c r="P37" s="17">
+        <f>IF(OR(P$25="",$A37="",NOT(ISNUMBER(P18)),NOT(ISNUMBER(O18)),N(O18)=0),"",P18/O18-1)</f>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <f>IF(OR(A19="",A20=""),"",A19)</f>
+      </c>
+      <c r="B38" s="17">
+        <f>IF(OR(B$25="",$A38="",NOT(ISNUMBER(B19)),NOT(ISNUMBER(A19)),N(A19)=0),"",B19/A19-1)</f>
+      </c>
+      <c r="C38" s="17">
+        <f>IF(OR(C$25="",$A38="",NOT(ISNUMBER(C19)),NOT(ISNUMBER(B19)),N(B19)=0),"",C19/B19-1)</f>
+      </c>
+      <c r="D38" s="17">
+        <f>IF(OR(D$25="",$A38="",NOT(ISNUMBER(D19)),NOT(ISNUMBER(C19)),N(C19)=0),"",D19/C19-1)</f>
+      </c>
+      <c r="E38" s="17">
+        <f>IF(OR(E$25="",$A38="",NOT(ISNUMBER(E19)),NOT(ISNUMBER(D19)),N(D19)=0),"",E19/D19-1)</f>
+      </c>
+      <c r="F38" s="17">
+        <f>IF(OR(F$25="",$A38="",NOT(ISNUMBER(F19)),NOT(ISNUMBER(E19)),N(E19)=0),"",F19/E19-1)</f>
+      </c>
+      <c r="G38" s="17">
+        <f>IF(OR(G$25="",$A38="",NOT(ISNUMBER(G19)),NOT(ISNUMBER(F19)),N(F19)=0),"",G19/F19-1)</f>
+      </c>
+      <c r="H38" s="17">
+        <f>IF(OR(H$25="",$A38="",NOT(ISNUMBER(H19)),NOT(ISNUMBER(G19)),N(G19)=0),"",H19/G19-1)</f>
+      </c>
+      <c r="I38" s="17">
+        <f>IF(OR(I$25="",$A38="",NOT(ISNUMBER(I19)),NOT(ISNUMBER(H19)),N(H19)=0),"",I19/H19-1)</f>
+      </c>
+      <c r="J38" s="17">
+        <f>IF(OR(J$25="",$A38="",NOT(ISNUMBER(J19)),NOT(ISNUMBER(I19)),N(I19)=0),"",J19/I19-1)</f>
+      </c>
+      <c r="K38" s="17">
+        <f>IF(OR(K$25="",$A38="",NOT(ISNUMBER(K19)),NOT(ISNUMBER(J19)),N(J19)=0),"",K19/J19-1)</f>
+      </c>
+      <c r="L38" s="17">
+        <f>IF(OR(L$25="",$A38="",NOT(ISNUMBER(L19)),NOT(ISNUMBER(K19)),N(K19)=0),"",L19/K19-1)</f>
+      </c>
+      <c r="M38" s="17">
+        <f>IF(OR(M$25="",$A38="",NOT(ISNUMBER(M19)),NOT(ISNUMBER(L19)),N(L19)=0),"",M19/L19-1)</f>
+      </c>
+      <c r="N38" s="17">
+        <f>IF(OR(N$25="",$A38="",NOT(ISNUMBER(N19)),NOT(ISNUMBER(M19)),N(M19)=0),"",N19/M19-1)</f>
+      </c>
+      <c r="O38" s="17">
+        <f>IF(OR(O$25="",$A38="",NOT(ISNUMBER(O19)),NOT(ISNUMBER(N19)),N(N19)=0),"",O19/N19-1)</f>
+      </c>
+      <c r="P38" s="17">
+        <f>IF(OR(P$25="",$A38="",NOT(ISNUMBER(P19)),NOT(ISNUMBER(O19)),N(O19)=0),"",P19/O19-1)</f>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <f>IF(OR(A20="",A21=""),"",A20)</f>
+      </c>
+      <c r="B39" s="17">
+        <f>IF(OR(B$25="",$A39="",NOT(ISNUMBER(B20)),NOT(ISNUMBER(A20)),N(A20)=0),"",B20/A20-1)</f>
+      </c>
+      <c r="C39" s="17">
+        <f>IF(OR(C$25="",$A39="",NOT(ISNUMBER(C20)),NOT(ISNUMBER(B20)),N(B20)=0),"",C20/B20-1)</f>
+      </c>
+      <c r="D39" s="17">
+        <f>IF(OR(D$25="",$A39="",NOT(ISNUMBER(D20)),NOT(ISNUMBER(C20)),N(C20)=0),"",D20/C20-1)</f>
+      </c>
+      <c r="E39" s="17">
+        <f>IF(OR(E$25="",$A39="",NOT(ISNUMBER(E20)),NOT(ISNUMBER(D20)),N(D20)=0),"",E20/D20-1)</f>
+      </c>
+      <c r="F39" s="17">
+        <f>IF(OR(F$25="",$A39="",NOT(ISNUMBER(F20)),NOT(ISNUMBER(E20)),N(E20)=0),"",F20/E20-1)</f>
+      </c>
+      <c r="G39" s="17">
+        <f>IF(OR(G$25="",$A39="",NOT(ISNUMBER(G20)),NOT(ISNUMBER(F20)),N(F20)=0),"",G20/F20-1)</f>
+      </c>
+      <c r="H39" s="17">
+        <f>IF(OR(H$25="",$A39="",NOT(ISNUMBER(H20)),NOT(ISNUMBER(G20)),N(G20)=0),"",H20/G20-1)</f>
+      </c>
+      <c r="I39" s="17">
+        <f>IF(OR(I$25="",$A39="",NOT(ISNUMBER(I20)),NOT(ISNUMBER(H20)),N(H20)=0),"",I20/H20-1)</f>
+      </c>
+      <c r="J39" s="17">
+        <f>IF(OR(J$25="",$A39="",NOT(ISNUMBER(J20)),NOT(ISNUMBER(I20)),N(I20)=0),"",J20/I20-1)</f>
+      </c>
+      <c r="K39" s="17">
+        <f>IF(OR(K$25="",$A39="",NOT(ISNUMBER(K20)),NOT(ISNUMBER(J20)),N(J20)=0),"",K20/J20-1)</f>
+      </c>
+      <c r="L39" s="17">
+        <f>IF(OR(L$25="",$A39="",NOT(ISNUMBER(L20)),NOT(ISNUMBER(K20)),N(K20)=0),"",L20/K20-1)</f>
+      </c>
+      <c r="M39" s="17">
+        <f>IF(OR(M$25="",$A39="",NOT(ISNUMBER(M20)),NOT(ISNUMBER(L20)),N(L20)=0),"",M20/L20-1)</f>
+      </c>
+      <c r="N39" s="17">
+        <f>IF(OR(N$25="",$A39="",NOT(ISNUMBER(N20)),NOT(ISNUMBER(M20)),N(M20)=0),"",N20/M20-1)</f>
+      </c>
+      <c r="O39" s="17">
+        <f>IF(OR(O$25="",$A39="",NOT(ISNUMBER(O20)),NOT(ISNUMBER(N20)),N(N20)=0),"",O20/N20-1)</f>
+      </c>
+      <c r="P39" s="17">
+        <f>IF(OR(P$25="",$A39="",NOT(ISNUMBER(P20)),NOT(ISNUMBER(O20)),N(O20)=0),"",P20/O20-1)</f>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <f>IF(OR(A21="",A22=""),"",A21)</f>
+      </c>
+      <c r="B40" s="17">
+        <f>IF(OR(B$25="",$A40="",NOT(ISNUMBER(B21)),NOT(ISNUMBER(A21)),N(A21)=0),"",B21/A21-1)</f>
+      </c>
+      <c r="C40" s="17">
+        <f>IF(OR(C$25="",$A40="",NOT(ISNUMBER(C21)),NOT(ISNUMBER(B21)),N(B21)=0),"",C21/B21-1)</f>
+      </c>
+      <c r="D40" s="17">
+        <f>IF(OR(D$25="",$A40="",NOT(ISNUMBER(D21)),NOT(ISNUMBER(C21)),N(C21)=0),"",D21/C21-1)</f>
+      </c>
+      <c r="E40" s="17">
+        <f>IF(OR(E$25="",$A40="",NOT(ISNUMBER(E21)),NOT(ISNUMBER(D21)),N(D21)=0),"",E21/D21-1)</f>
+      </c>
+      <c r="F40" s="17">
+        <f>IF(OR(F$25="",$A40="",NOT(ISNUMBER(F21)),NOT(ISNUMBER(E21)),N(E21)=0),"",F21/E21-1)</f>
+      </c>
+      <c r="G40" s="17">
+        <f>IF(OR(G$25="",$A40="",NOT(ISNUMBER(G21)),NOT(ISNUMBER(F21)),N(F21)=0),"",G21/F21-1)</f>
+      </c>
+      <c r="H40" s="17">
+        <f>IF(OR(H$25="",$A40="",NOT(ISNUMBER(H21)),NOT(ISNUMBER(G21)),N(G21)=0),"",H21/G21-1)</f>
+      </c>
+      <c r="I40" s="17">
+        <f>IF(OR(I$25="",$A40="",NOT(ISNUMBER(I21)),NOT(ISNUMBER(H21)),N(H21)=0),"",I21/H21-1)</f>
+      </c>
+      <c r="J40" s="17">
+        <f>IF(OR(J$25="",$A40="",NOT(ISNUMBER(J21)),NOT(ISNUMBER(I21)),N(I21)=0),"",J21/I21-1)</f>
+      </c>
+      <c r="K40" s="17">
+        <f>IF(OR(K$25="",$A40="",NOT(ISNUMBER(K21)),NOT(ISNUMBER(J21)),N(J21)=0),"",K21/J21-1)</f>
+      </c>
+      <c r="L40" s="17">
+        <f>IF(OR(L$25="",$A40="",NOT(ISNUMBER(L21)),NOT(ISNUMBER(K21)),N(K21)=0),"",L21/K21-1)</f>
+      </c>
+      <c r="M40" s="17">
+        <f>IF(OR(M$25="",$A40="",NOT(ISNUMBER(M21)),NOT(ISNUMBER(L21)),N(L21)=0),"",M21/L21-1)</f>
+      </c>
+      <c r="N40" s="17">
+        <f>IF(OR(N$25="",$A40="",NOT(ISNUMBER(N21)),NOT(ISNUMBER(M21)),N(M21)=0),"",N21/M21-1)</f>
+      </c>
+      <c r="O40" s="17">
+        <f>IF(OR(O$25="",$A40="",NOT(ISNUMBER(O21)),NOT(ISNUMBER(N21)),N(N21)=0),"",O21/N21-1)</f>
+      </c>
+      <c r="P40" s="17">
+        <f>IF(OR(P$25="",$A40="",NOT(ISNUMBER(P21)),NOT(ISNUMBER(O21)),N(O21)=0),"",P21/O21-1)</f>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total (meses comparables)</t>
+        </is>
+      </c>
+      <c r="B41" s="17">
+        <f>IF(B$25="","",IFERROR(SUMPRODUCT(ISNUMBER(B7:B21)*ISNUMBER(A7:A21)*($A8:$A22&lt;&gt;""),B7:B21)/SUMPRODUCT(ISNUMBER(B7:B21)*ISNUMBER(A7:A21)*($A8:$A22&lt;&gt;""),A7:A21)-1,""))</f>
+      </c>
+      <c r="C41" s="17">
+        <f>IF(C$25="","",IFERROR(SUMPRODUCT(ISNUMBER(C7:C21)*ISNUMBER(B7:B21)*($A8:$A22&lt;&gt;""),C7:C21)/SUMPRODUCT(ISNUMBER(C7:C21)*ISNUMBER(B7:B21)*($A8:$A22&lt;&gt;""),B7:B21)-1,""))</f>
+      </c>
+      <c r="D41" s="17">
+        <f>IF(D$25="","",IFERROR(SUMPRODUCT(ISNUMBER(D7:D21)*ISNUMBER(C7:C21)*($A8:$A22&lt;&gt;""),D7:D21)/SUMPRODUCT(ISNUMBER(D7:D21)*ISNUMBER(C7:C21)*($A8:$A22&lt;&gt;""),C7:C21)-1,""))</f>
+      </c>
+      <c r="E41" s="17">
+        <f>IF(E$25="","",IFERROR(SUMPRODUCT(ISNUMBER(E7:E21)*ISNUMBER(D7:D21)*($A8:$A22&lt;&gt;""),E7:E21)/SUMPRODUCT(ISNUMBER(E7:E21)*ISNUMBER(D7:D21)*($A8:$A22&lt;&gt;""),D7:D21)-1,""))</f>
+      </c>
+      <c r="F41" s="17">
+        <f>IF(F$25="","",IFERROR(SUMPRODUCT(ISNUMBER(F7:F21)*ISNUMBER(E7:E21)*($A8:$A22&lt;&gt;""),F7:F21)/SUMPRODUCT(ISNUMBER(F7:F21)*ISNUMBER(E7:E21)*($A8:$A22&lt;&gt;""),E7:E21)-1,""))</f>
+      </c>
+      <c r="G41" s="17">
+        <f>IF(G$25="","",IFERROR(SUMPRODUCT(ISNUMBER(G7:G21)*ISNUMBER(F7:F21)*($A8:$A22&lt;&gt;""),G7:G21)/SUMPRODUCT(ISNUMBER(G7:G21)*ISNUMBER(F7:F21)*($A8:$A22&lt;&gt;""),F7:F21)-1,""))</f>
+      </c>
+      <c r="H41" s="17">
+        <f>IF(H$25="","",IFERROR(SUMPRODUCT(ISNUMBER(H7:H21)*ISNUMBER(G7:G21)*($A8:$A22&lt;&gt;""),H7:H21)/SUMPRODUCT(ISNUMBER(H7:H21)*ISNUMBER(G7:G21)*($A8:$A22&lt;&gt;""),G7:G21)-1,""))</f>
+      </c>
+      <c r="I41" s="17">
+        <f>IF(I$25="","",IFERROR(SUMPRODUCT(ISNUMBER(I7:I21)*ISNUMBER(H7:H21)*($A8:$A22&lt;&gt;""),I7:I21)/SUMPRODUCT(ISNUMBER(I7:I21)*ISNUMBER(H7:H21)*($A8:$A22&lt;&gt;""),H7:H21)-1,""))</f>
+      </c>
+      <c r="J41" s="17">
+        <f>IF(J$25="","",IFERROR(SUMPRODUCT(ISNUMBER(J7:J21)*ISNUMBER(I7:I21)*($A8:$A22&lt;&gt;""),J7:J21)/SUMPRODUCT(ISNUMBER(J7:J21)*ISNUMBER(I7:I21)*($A8:$A22&lt;&gt;""),I7:I21)-1,""))</f>
+      </c>
+      <c r="K41" s="17">
+        <f>IF(K$25="","",IFERROR(SUMPRODUCT(ISNUMBER(K7:K21)*ISNUMBER(J7:J21)*($A8:$A22&lt;&gt;""),K7:K21)/SUMPRODUCT(ISNUMBER(K7:K21)*ISNUMBER(J7:J21)*($A8:$A22&lt;&gt;""),J7:J21)-1,""))</f>
+      </c>
+      <c r="L41" s="17">
+        <f>IF(L$25="","",IFERROR(SUMPRODUCT(ISNUMBER(L7:L21)*ISNUMBER(K7:K21)*($A8:$A22&lt;&gt;""),L7:L21)/SUMPRODUCT(ISNUMBER(L7:L21)*ISNUMBER(K7:K21)*($A8:$A22&lt;&gt;""),K7:K21)-1,""))</f>
+      </c>
+      <c r="M41" s="17">
+        <f>IF(M$25="","",IFERROR(SUMPRODUCT(ISNUMBER(M7:M21)*ISNUMBER(L7:L21)*($A8:$A22&lt;&gt;""),M7:M21)/SUMPRODUCT(ISNUMBER(M7:M21)*ISNUMBER(L7:L21)*($A8:$A22&lt;&gt;""),L7:L21)-1,""))</f>
+      </c>
+      <c r="N41" s="17">
+        <f>IF(N$25="","",IFERROR(SUMPRODUCT(ISNUMBER(N7:N21)*ISNUMBER(M7:M21)*($A8:$A22&lt;&gt;""),N7:N21)/SUMPRODUCT(ISNUMBER(N7:N21)*ISNUMBER(M7:M21)*($A8:$A22&lt;&gt;""),M7:M21)-1,""))</f>
+      </c>
+      <c r="O41" s="17">
+        <f>IF(O$25="","",IFERROR(SUMPRODUCT(ISNUMBER(O7:O21)*ISNUMBER(N7:N21)*($A8:$A22&lt;&gt;""),O7:O21)/SUMPRODUCT(ISNUMBER(O7:O21)*ISNUMBER(N7:N21)*($A8:$A22&lt;&gt;""),N7:N21)-1,""))</f>
+      </c>
+      <c r="P41" s="17">
+        <f>IF(P$25="","",IFERROR(SUMPRODUCT(ISNUMBER(P7:P21)*ISNUMBER(O7:O21)*($A8:$A22&lt;&gt;""),P7:P21)/SUMPRODUCT(ISNUMBER(P7:P21)*ISNUMBER(O7:O21)*($A8:$A22&lt;&gt;""),O7:O21)-1,""))</f>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B26:P41">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D558"/>

--- a/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
+++ b/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
@@ -176,28 +176,28 @@
     <t>Suma de unidades</t>
   </si>
   <si>
-    <t>Listado de productos comprados agrupados por el número de veces comprado. Incluye promedios sobre el producto</t>
+    <t>Productos ordenados por el nº de veces que se han comprado (cada línea de ticket cuenta una vez), con su precio medio por unidad. Los productos a peso no tienen precio por unidad y salen vacíos.</t>
   </si>
   <si>
-    <t>Número de productos comprados al mes. Con gráfica</t>
+    <t>Unidades compradas por año y mes, en tabla y gráfica. El filtro id permite ver uno o varios productos; sin filtro suma todos. Los productos a peso cuentan 1 unidad por compra.</t>
   </si>
   <si>
-    <t>Dinero gastado al mes. Con gráfica</t>
+    <t>Gasto total (€) por año y mes, en tabla y gráfica, sumando todas las compras. Sirve para ver qué meses se gasta más y cómo evoluciona el gasto.</t>
   </si>
   <si>
-    <t>Ultima vez que se compró un producto</t>
+    <t>Fecha de la última compra de cada producto. Sirve para detectar productos que llevan más tiempo del habitual sin comprarse.</t>
   </si>
   <si>
-    <t>Evolución del precio de un producto promediado al mes. En el selector se fija el producto y permite ver como ha evolucionado su precio con el tiempo</t>
+    <t>Precio medio por unidad de un producto, mes a mes, en tabla y gráfica. Elige un único producto en el filtro id (con varios la media los mezcla). Los productos a peso no tienen precio por unidad.</t>
   </si>
   <si>
-    <t>Promedio por mes de unidades de un producto. Con selectores para fijar el producto y el mes</t>
+    <t>Unidades compradas de cada producto, de más a menos. El filtro fecha elige un mes del año (suma ese mes de todos los años) para ver qué se compra más en cada época.</t>
   </si>
   <si>
-    <t>Número de productos comprados al año. Especie de bolsa de la compara anual. Muestra cuanto se ha gastado en ese producto al año</t>
+    <t>La cesta de la compra de cada año: qué productos se compraron, cuántas veces (líneas de ticket) y cuánto se gastó (€) en cada uno.</t>
   </si>
   <si>
-    <t>Esto se un cáculo de la inflación sufrida por los productos comprados. No es la inflación calculada por el INE</t>
+    <t>Inflación de tu propia cesta de la compra (no es el IPC del INE): % de variación de precios frente al año base. Laspeyres pondera con lo comprado el año base; Paasche, con lo comprado cada año. Solo cuentan los productos comprados en ambos años (Productos coincidentes).</t>
   </si>
   <si>
     <t>Año</t>
@@ -218,7 +218,7 @@
     <t>Productos coincidentes</t>
   </si>
   <si>
-    <t>Evolución de la cantidad de productos comprados en un año. En el selector se fija el producto y permite ver como ha evolucionadoel número de productos comprados</t>
+    <t>Unidades compradas de un producto cada año, en tabla y gráfica. Elige el producto en el filtro id (sin filtro suma todos). El primer y el último año pueden estar incompletos.</t>
   </si>
 </sst>
 </file>

--- a/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
+++ b/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
@@ -5241,13 +5241,13 @@
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámicaPareto" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A7:D10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <location ref="A7:D11" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending" defaultSubtotal="0">
       <items count="3">
         <item x="0"/>
         <item x="1"/>
-        <item x="2" h="1"/>
+        <item x="2"/>
       </items>
       <autoSortScope>
         <pivotArea dataOnly="0" outline="0" fieldPosition="0">
@@ -5294,12 +5294,15 @@
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="4">
     <i>
       <x/>
     </i>
     <i>
       <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
     </i>
     <i t="grand">
       <x/>

--- a/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
+++ b/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
@@ -26,9 +26,10 @@
     <sheet name="Evolucion-N" sheetId="17" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Datos!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Datos!$A$1:$H$3</definedName>
     <definedName name="compras_mercadona" localSheetId="0">Datos!#REF!</definedName>
     <definedName name="export_personal_dataa" localSheetId="0">Datos!$A$1:$G$3</definedName>
+    <definedName name="DatosTablaDinamica">OFFSET(Datos!$A$1,0,0,1048576,COUNTA(Datos!$1:$1))</definedName>
   </definedNames>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
   <pivotCaches>
@@ -225,8 +226,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ hh:mm"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -318,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -343,6 +345,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4310,9 +4313,9 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshOnLoad="1" refreshedBy="dserrada@gmail.com" refreshedDate="46277.655617592594" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="3">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:G1048576" sheet="Datos"/>
+    <worksheetSource name="DatosTablaDinamica"/>
   </cacheSource>
-  <cacheFields count="8">
+  <cacheFields count="9">
     <cacheField name="id" numFmtId="0">
       <sharedItems containsBlank="1" count="3">
         <s v="COCKTAIL RODEO"/>
@@ -4326,7 +4329,7 @@
         <d v="2023-06-17T00:00:00"/>
         <m/>
       </sharedItems>
-      <fieldGroup par="7" base="1">
+      <fieldGroup par="8" base="1">
         <rangePr groupBy="months" startDate="2023-06-16T00:00:00" endDate="2023-06-18T00:00:00"/>
         <groupItems count="14">
           <s v="(en blanco)"/>
@@ -4361,6 +4364,13 @@
     <cacheField name="precio" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.48" maxValue="3.5"/>
     </cacheField>
+    <cacheField name="factura" numFmtId="0">
+      <sharedItems containsBlank="1" count="3">
+        <s v="0000-000-000001"/>
+        <s v="0000-000-000002"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
     <cacheField name="Años" numFmtId="0" databaseField="0">
       <fieldGroup base="1">
         <rangePr groupBy="years" startDate="2023-06-16T00:00:00" endDate="2023-06-18T00:00:00"/>
@@ -4390,6 +4400,7 @@
     <m/>
     <m/>
     <n v="3.5"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="1"/>
@@ -4399,6 +4410,7 @@
     <m/>
     <m/>
     <n v="0.48"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="2"/>
@@ -4408,6 +4420,7 @@
     <m/>
     <m/>
     <m/>
+    <x v="2"/>
   </r>
 </pivotCacheRecords>
 </file>
@@ -4415,7 +4428,7 @@
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:C8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
+  <pivotFields count="9">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending" defaultSubtotal="0">
       <items count="3">
         <item x="1"/>
@@ -4453,6 +4466,7 @@
     </pivotField>
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
@@ -4508,7 +4522,7 @@
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámicaInteranual" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:C8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="8">
+  <pivotFields count="9">
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
       <items count="14">
@@ -4533,6 +4547,7 @@
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
       <items count="3">
         <item x="0"/>
@@ -4553,7 +4568,7 @@
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="7"/>
+    <field x="8"/>
   </colFields>
   <colItems count="2">
     <i>
@@ -4578,7 +4593,7 @@
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A4:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
+  <pivotFields count="9">
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="15">
@@ -4604,6 +4619,7 @@
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
       <items count="3">
         <item x="0"/>
@@ -4613,7 +4629,7 @@
     </pivotField>
   </pivotFields>
   <rowFields count="2">
-    <field x="7"/>
+    <field x="8"/>
     <field x="1"/>
   </rowFields>
   <rowItems count="5">
@@ -4682,7 +4698,7 @@
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A4:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="8">
+  <pivotFields count="9">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
       <items count="3">
         <item x="1"/>
@@ -4714,6 +4730,7 @@
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
       <items count="3">
         <item x="0"/>
@@ -4723,7 +4740,7 @@
     </pivotField>
   </pivotFields>
   <rowFields count="2">
-    <field x="7"/>
+    <field x="8"/>
     <field x="1"/>
   </rowFields>
   <rowItems count="5">
@@ -4795,7 +4812,7 @@
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica4" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A7:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="8">
+  <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0" sortType="descending" defaultSubtotal="0">
       <items count="3">
         <item x="1"/>
@@ -4832,6 +4849,7 @@
       </items>
     </pivotField>
     <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
@@ -4893,7 +4911,7 @@
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:C10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
+  <pivotFields count="9">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
       <items count="4">
         <item x="1"/>
@@ -4935,6 +4953,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
       <items count="3">
         <item x="0"/>
@@ -4944,7 +4963,7 @@
     </pivotField>
   </pivotFields>
   <rowFields count="2">
-    <field x="7"/>
+    <field x="8"/>
     <field x="0"/>
   </rowFields>
   <rowItems count="6">
@@ -4994,7 +5013,7 @@
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
+  <pivotFields count="9">
     <pivotField axis="axisRow" multipleItemSelectionAllowed="1" showAll="0" sortType="descending">
       <items count="4">
         <item x="1"/>
@@ -5036,6 +5055,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0">
       <items count="3">
         <item x="0"/>
@@ -5079,7 +5099,7 @@
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A6:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="8">
+  <pivotFields count="9">
     <pivotField axis="axisPage" showAll="0">
       <items count="4">
         <item x="1"/>
@@ -5112,6 +5132,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
       <items count="3">
         <item x="0"/>
@@ -5121,7 +5142,7 @@
     </pivotField>
   </pivotFields>
   <rowFields count="2">
-    <field x="7"/>
+    <field x="8"/>
     <field x="1"/>
   </rowFields>
   <rowItems count="5">
@@ -5173,7 +5194,7 @@
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A6:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="8">
+  <pivotFields count="9">
     <pivotField axis="axisPage" showAll="0">
       <items count="4">
         <item x="1"/>
@@ -5188,6 +5209,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
       <items count="3">
         <item x="0"/>
@@ -5197,7 +5219,7 @@
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="7"/>
+    <field x="8"/>
   </rowFields>
   <rowItems count="3">
     <i>
@@ -5242,7 +5264,7 @@
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámicaPareto" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A7:D11" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="8">
+  <pivotFields count="9">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending" defaultSubtotal="0">
       <items count="3">
         <item x="0"/>
@@ -5283,6 +5305,7 @@
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
       <items count="3">
         <item x="0"/>
@@ -5323,7 +5346,7 @@
     </i>
   </colItems>
   <pageFields count="1">
-    <pageField fld="7" hier="-1"/>
+    <pageField fld="8" hier="-1"/>
   </pageFields>
   <dataFields count="3">
     <dataField name="Gasto" fld="6" baseField="0" baseItem="0" numFmtId="164"/>
@@ -5602,19 +5625,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" style="18" customWidth="1"/>
     <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -5636,12 +5660,17 @@
       <c r="G1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>factura</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="18">
         <v>45093</v>
       </c>
       <c r="C2">
@@ -5653,12 +5682,17 @@
       <c r="G2">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0000-000-000001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="18">
         <v>45094</v>
       </c>
       <c r="C3">
@@ -5670,9 +5704,14 @@
       <c r="G3">
         <v>0.48</v>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0000-000-000002</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:H3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
+++ b/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
@@ -13,6 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="6" r:id="rId1"/>
+    <sheet name="Facturas" sheetId="20" r:id="rId17"/>
     <sheet name="Productos" sheetId="7" r:id="rId2"/>
     <sheet name="Pareto" sheetId="18" r:id="rId15"/>
     <sheet name="MiInflación" sheetId="16" r:id="rId3"/>
@@ -24,16 +25,19 @@
     <sheet name="Último" sheetId="13" r:id="rId8"/>
     <sheet name="Evolucion-€" sheetId="14" r:id="rId9"/>
     <sheet name="Evolucion-N" sheetId="17" r:id="rId10"/>
+    <sheet name="FacturasUnid" sheetId="21" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Datos!$A$1:$H$3</definedName>
     <definedName name="compras_mercadona" localSheetId="0">Datos!#REF!</definedName>
     <definedName name="export_personal_dataa" localSheetId="0">Datos!$A$1:$G$3</definedName>
     <definedName name="DatosTablaDinamica">OFFSET(Datos!$A$1,0,0,1048576,COUNTA(Datos!$1:$1))</definedName>
+    <definedName name="FacturasTablaDinamica">OFFSET(Facturas!$A$1,0,0,COUNTA(Facturas!$A:$A),COUNTA(Facturas!$1:$1))</definedName>
   </definedNames>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
   <pivotCaches>
     <pivotCache cacheId="4" r:id="rId11"/>
+    <pivotCache cacheId="5" r:id="rId19"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -4390,6 +4394,44 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshOnLoad="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="2">
+  <cacheSource type="worksheet">
+    <worksheetSource name="FacturasTablaDinamica"/>
+  </cacheSource>
+  <cacheFields count="6">
+    <cacheField name="factura" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="fecha" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-06-16T00:00:00" maxDate="2023-06-17T00:00:00"/>
+    </cacheField>
+    <cacheField name="año" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2023" maxValue="2023" count="1">
+        <n v="2023"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="lineas" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
+    </cacheField>
+    <cacheField name="unidades" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="2"/>
+      <fieldGroup base="4">
+        <rangePr autoStart="0" startNum="0" endNum="2" groupInterval="10"/>
+        <groupItems count="3">
+          <s v="&lt;0"/>
+          <s v="0-9"/>
+          <s v="&gt;10"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="importe" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.48" maxValue="3.5"/>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="3">
   <r>
@@ -4421,6 +4463,27 @@
     <m/>
     <m/>
     <x v="2"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="2">
+  <r>
+    <s v="0000-000-000001"/>
+    <d v="2023-06-16T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="2"/>
+    <n v="3.5"/>
+  </r>
+  <r>
+    <s v="0000-000-000002"/>
+    <d v="2023-06-17T00:00:00"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0.48"/>
   </r>
 </pivotCacheRecords>
 </file>
@@ -4587,6 +4650,66 @@
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
   </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámicaFacturasUnid" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Unidades por ticket">
+  <location ref="A7:D9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="6">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="2" hier="-1"/>
+  </pageFields>
+  <dataFields count="3">
+    <dataField name="Facturas" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="% facturas" fld="0" subtotal="count" showDataAs="percentOfCol" baseField="0" baseItem="0" numFmtId="10"/>
+    <dataField name="Importe medio" fld="5" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
 </pivotTableDefinition>
 </file>
 
@@ -22799,6 +22922,168 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" style="18" customWidth="1"/>
+    <col min="3" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="6" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">factura</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fecha</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">año</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lineas</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unidades</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">importe</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0000-000-000001</t>
+        </is>
+      </c>
+      <c r="B2" s="18">
+        <v>45093</v>
+      </c>
+      <c r="C2">
+        <v>2023</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2" s="6">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0000-000-000002</t>
+        </is>
+      </c>
+      <c r="B3" s="18">
+        <v>45094</v>
+      </c>
+      <c r="C3">
+        <v>2023</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0.48</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="4" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Facturas por número de unidades</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuántos tickets hay según las unidades compradas en cada uno (de 10 en 10: 0-9, 10-19...), con su peso sobre el total y el importe medio del ticket en ese rango. Separa las compras pequeñas de reposición de las compras grandes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Un producto a peso cuenta como 1 unidad. Para cambiar el tamaño del rango: botón derecho sobre la columna de rangos &gt; Agrupar. Datos de origen: hoja Facturas (una fila por ticket).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">año</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(Todas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unidades por ticket</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Facturas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">% facturas</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Importe medio</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D558"/>

--- a/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
+++ b/projects/ticket-digital-data/src/main/resources/Mercadona-base.xlsx
@@ -18,6 +18,7 @@
     <sheet name="Pareto" sheetId="18" r:id="rId15"/>
     <sheet name="MiInflación" sheetId="16" r:id="rId3"/>
     <sheet name="Interanual" sheetId="19" r:id="rId16"/>
+    <sheet name="MapaCalor" sheetId="22" r:id="rId20"/>
     <sheet name="T_Precio" sheetId="8" r:id="rId4"/>
     <sheet name="T_Cantidad" sheetId="15" r:id="rId5"/>
     <sheet name="Mes" sheetId="10" r:id="rId6"/>
@@ -4713,6 +4714,113 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámicaMapaCalor" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A6:B10" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending" defaultSubtotal="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
+      <items count="14">
+        <item x="0" h="1"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+  </rowItems>
+  <colFields count="2">
+    <field x="8"/>
+    <field x="1"/>
+  </colFields>
+  <colItems count="1">
+    <i>
+      <x v="1"/>
+      <x v="6"/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Gasto" fld="6" baseField="0" baseItem="0" numFmtId="1"/>
+  </dataFields>
+  <conditionalFormats count="1">
+    <conditionalFormat scope="data" priority="1">
+      <pivotAreas count="1">
+        <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="50" filterVal="50"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A4:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
@@ -23084,6 +23192,60 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="200" width="6.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mapa de calor: gasto por producto y mes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qué se mide: gasto mensual de cada producto, en € redondeados a la unidad (suma de lo pagado por ese producto en el mes). Filas: los 50 productos con más gasto en todo el periodo, de mayor a menor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Color: cuanto más rojo, más gasto ese mes, comparado con el resto de la tabla; en blanco, ese mes no se compró. Sirve para ver cambios de hábito (productos que desaparecen o que entran fuerte) y la estacionalidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Para ver más o menos productos: filtro de la fila → Filtros de valor → Diez mejores.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B9:B10" pivot="1">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FFFCC98F"/>
+        <color rgb="FFE0503C"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D558"/>
